--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132097248</v>
       </c>
       <c r="B2" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132097247</v>
       </c>
       <c r="B3" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>132097252</v>
       </c>
       <c r="B4" t="n">
-        <v>97915</v>
+        <v>97920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132097248</v>
       </c>
       <c r="B2" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132097247</v>
       </c>
       <c r="B3" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>132097252</v>
       </c>
       <c r="B4" t="n">
-        <v>97920</v>
+        <v>97922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132097248</v>
       </c>
       <c r="B2" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132097247</v>
       </c>
       <c r="B3" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>132097252</v>
       </c>
       <c r="B4" t="n">
-        <v>97922</v>
+        <v>97958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132097248</v>
       </c>
       <c r="B2" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132097247</v>
       </c>
       <c r="B3" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>132097252</v>
       </c>
       <c r="B4" t="n">
-        <v>97963</v>
+        <v>97966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132097248</v>
       </c>
       <c r="B2" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132097247</v>
       </c>
       <c r="B3" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>132097252</v>
       </c>
       <c r="B4" t="n">
-        <v>97966</v>
+        <v>97974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132097248</v>
       </c>
       <c r="B2" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132097247</v>
       </c>
       <c r="B3" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>132097252</v>
       </c>
       <c r="B4" t="n">
-        <v>97974</v>
+        <v>97984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132097248</v>
       </c>
       <c r="B2" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132097247</v>
       </c>
       <c r="B3" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>132097252</v>
       </c>
       <c r="B4" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132097248</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132097247</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>132097252</v>
       </c>
       <c r="B4" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132097248</v>
       </c>
       <c r="B2" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>132097247</v>
       </c>
       <c r="B3" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>132097252</v>
       </c>
       <c r="B4" t="n">
-        <v>97987</v>
+        <v>97989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132097248</v>
+        <v>132097247</v>
       </c>
       <c r="B2" t="n">
-        <v>93200</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582286</v>
+        <v>582334</v>
       </c>
       <c r="R2" t="n">
-        <v>6536654</v>
+        <v>6536602</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,14 +789,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132097247</v>
+        <v>132097248</v>
       </c>
       <c r="B3" t="n">
-        <v>93200</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582334</v>
+        <v>582286</v>
       </c>
       <c r="R3" t="n">
-        <v>6536602</v>
+        <v>6536654</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132097252</v>
+        <v>132097251</v>
       </c>
       <c r="B4" t="n">
-        <v>97989</v>
+        <v>98063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582034</v>
+        <v>582008</v>
       </c>
       <c r="R4" t="n">
-        <v>6536646</v>
+        <v>6536603</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,6 +1011,117 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132097252</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vikstugan, Vikstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>582034</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6536646</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16435-2026 artfynd.xlsx
+++ b/artfynd/A 16435-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132097247</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132097248</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132097251</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,8 +1142,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132097252</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>